--- a/inputs/Fund Mapping.xlsx
+++ b/inputs/Fund Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hclevenger\Desktop\Paul Asset Allocation\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25729C5-F39A-4E45-B504-563EAD0A196E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95097996-1E84-4297-881F-640E637F05CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4875" yWindow="945" windowWidth="21615" windowHeight="14910" activeTab="1" xr2:uid="{024060E7-508A-4828-BE3B-D4E1FF20B32E}"/>
   </bookViews>
@@ -265,12 +265,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,14 +765,10 @@
         <v>23</v>
       </c>
       <c r="B10" s="8"/>
-      <c r="F10" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0.1</v>
-      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
       <c r="H10" s="6">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -792,14 +786,10 @@
       </c>
       <c r="B12" s="8"/>
       <c r="F12" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0.2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1092,10 +1082,10 @@
         <v>8</v>
       </c>
       <c r="J7" s="6">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="K7" s="6">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1111,9 +1101,17 @@
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="F9" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0.25</v>
+      </c>
       <c r="I9" s="6">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1123,16 +1121,18 @@
       <c r="B10" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="6">
-        <v>0.5</v>
+      <c r="F10" s="13">
+        <v>0.25</v>
       </c>
       <c r="G10" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="H10" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="I10" s="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1142,10 +1142,10 @@
         <v>8</v>
       </c>
       <c r="J11" s="6">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="K11" s="6">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1167,15 +1167,15 @@
         <v>8</v>
       </c>
       <c r="J13" s="6">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="K13" s="6">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
+      <c r="B14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">

--- a/inputs/Fund Mapping.xlsx
+++ b/inputs/Fund Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hclevenger\Desktop\Paul Asset Allocation\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95097996-1E84-4297-881F-640E637F05CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4A4FFD-AED2-4D00-A039-A9B76D1BCEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4875" yWindow="945" windowWidth="21615" windowHeight="14910" activeTab="1" xr2:uid="{024060E7-508A-4828-BE3B-D4E1FF20B32E}"/>
+    <workbookView xWindow="4875" yWindow="945" windowWidth="21615" windowHeight="14910" xr2:uid="{024060E7-508A-4828-BE3B-D4E1FF20B32E}"/>
   </bookViews>
   <sheets>
     <sheet name="Fidelity" sheetId="2" r:id="rId1"/>
@@ -739,10 +739,10 @@
       </c>
       <c r="B7" s="8"/>
       <c r="J7" s="6">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="K7" s="6">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
       </c>
       <c r="B13" s="8"/>
       <c r="J13" s="6">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="K13" s="6">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -818,10 +818,10 @@
       </c>
       <c r="B15" s="8"/>
       <c r="J15" s="6">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="K15" s="6">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1167,10 +1167,10 @@
         <v>8</v>
       </c>
       <c r="J13" s="6">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="K13" s="6">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
